--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92994607148</v>
+        <v>46157.93082536795</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93082536795</v>
+        <v>46157.93352834527</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93352834527</v>
+        <v>46157.9364230525</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9364230525</v>
+        <v>46158.28177989274</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28177989274</v>
+        <v>46158.29754414855</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92964007309</v>
+        <v>46158.29719691163</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>46155.61217592593</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46157.92964007309</v>
+        <v>46158.29719691163</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29754414855</v>
+        <v>46158.29772696914</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29772696914</v>
+        <v>46158.30446524903</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446524903</v>
+        <v>46158.33341470899</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33341470899</v>
+        <v>46158.37202095707</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37202095707</v>
+        <v>46158.37418277694</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.29719691163</v>
+        <v>46158.37375972194</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>46155.61217592593</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46158.29719691163</v>
+        <v>46158.37375972194</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
